--- a/reference_templates/15_ข้อมูลโรงเรียนเอกชนนอกระบบ.xlsx
+++ b/reference_templates/15_ข้อมูลโรงเรียนเอกชนนอกระบบ.xlsx
@@ -2325,7 +2325,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31C1F5F4-787A-4CAE-BAC8-D9AA182DEE66}">
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.875" bestFit="1" customWidth="1"/>
@@ -2362,58 +2362,70 @@
       <c r="H2" s="37"/>
       <c r="I2" s="37"/>
     </row>
-    <row r="3" spans="1:11" s="38" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="4" spans="1:11" ht="48" x14ac:dyDescent="0.2">
-      <c r="A4" s="39" t="s">
+    <row r="3" spans="1:11" ht="48" x14ac:dyDescent="0.2">
+      <c r="A3" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="B4" s="40" t="s">
+      <c r="B3" s="40" t="s">
         <v>39</v>
       </c>
-      <c r="C4" s="40" t="s">
+      <c r="C3" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="41" t="s">
+      <c r="D3" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="41" t="s">
+      <c r="E3" s="41" t="s">
         <v>38</v>
       </c>
-      <c r="F4" s="42" t="s">
+      <c r="F3" s="42" t="s">
         <v>31</v>
       </c>
-      <c r="G4" s="43"/>
-      <c r="H4" s="44"/>
-      <c r="I4" s="42" t="s">
+      <c r="G3" s="43"/>
+      <c r="H3" s="44"/>
+      <c r="I3" s="42" t="s">
         <v>32</v>
       </c>
-      <c r="J4" s="43"/>
-      <c r="K4" s="45"/>
-    </row>
-    <row r="5" spans="1:11" ht="24" x14ac:dyDescent="0.2">
-      <c r="A5" s="46"/>
-      <c r="B5" s="35"/>
-      <c r="C5" s="35"/>
-      <c r="D5" s="35"/>
-      <c r="E5" s="35"/>
-      <c r="F5" s="36" t="s">
+      <c r="J3" s="43"/>
+      <c r="K3" s="45"/>
+    </row>
+    <row r="4" spans="1:11" ht="24" x14ac:dyDescent="0.2">
+      <c r="A4" s="46"/>
+      <c r="B4" s="35"/>
+      <c r="C4" s="35"/>
+      <c r="D4" s="35"/>
+      <c r="E4" s="35"/>
+      <c r="F4" s="36" t="s">
         <v>12</v>
       </c>
-      <c r="G5" s="36" t="s">
+      <c r="G4" s="36" t="s">
         <v>13</v>
       </c>
-      <c r="H5" s="36" t="s">
+      <c r="H4" s="36" t="s">
         <v>33</v>
       </c>
-      <c r="I5" s="36" t="s">
+      <c r="I4" s="36" t="s">
         <v>12</v>
       </c>
-      <c r="J5" s="36" t="s">
+      <c r="J4" s="36" t="s">
         <v>13</v>
       </c>
-      <c r="K5" s="47" t="s">
+      <c r="K4" s="47" t="s">
         <v>33</v>
       </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A5" s="34"/>
+      <c r="B5" s="34"/>
+      <c r="C5" s="34"/>
+      <c r="D5" s="34"/>
+      <c r="E5" s="34"/>
+      <c r="F5" s="34"/>
+      <c r="G5" s="34"/>
+      <c r="H5" s="34"/>
+      <c r="I5" s="34"/>
+      <c r="J5" s="34"/>
+      <c r="K5" s="34"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" s="34"/>
@@ -2545,23 +2557,10 @@
       <c r="J15" s="34"/>
       <c r="K15" s="34"/>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A16" s="34"/>
-      <c r="B16" s="34"/>
-      <c r="C16" s="34"/>
-      <c r="D16" s="34"/>
-      <c r="E16" s="34"/>
-      <c r="F16" s="34"/>
-      <c r="G16" s="34"/>
-      <c r="H16" s="34"/>
-      <c r="I16" s="34"/>
-      <c r="J16" s="34"/>
-      <c r="K16" s="34"/>
-    </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="F4:H4"/>
-    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="I3:K3"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup scale="80" orientation="landscape" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
